--- a/backend/volunteers/files/plantilla_voluntarios.xlsx
+++ b/backend/volunteers/files/plantilla_voluntarios.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perez\OneDrive - Universidad de Guadalajara\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perez\OneDrive - Universidad de Guadalajara\Desktop\gestion-voluntarios\backend\volunteers\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0C06768-0B6D-41F4-B8B3-F5E0E89BFB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A30839A-F964-4B63-B6B0-F4D851112AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -486,7 +486,7 @@
       <c r="F6" s="3"/>
     </row>
   </sheetData>
-  <dataValidations xWindow="38" yWindow="332" count="9">
+  <dataValidations xWindow="38" yWindow="332" count="10">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="InicialesNombreApellidos-Año-Num" prompt="Ej. FGS-2026-0382" sqref="A2" xr:uid="{F0EC90C0-1A64-46E6-9C6E-6455011B6002}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Ej. Felipe" sqref="B2" xr:uid="{B233B401-842B-49F5-BA8B-9DD10B82C2F0}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Ej. Alfredo" sqref="C2" xr:uid="{543CC531-5717-4CE8-8D9C-4800DF39C22A}"/>
@@ -496,6 +496,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="F para femenino M para masculino" prompt="Ej. M" sqref="G2" xr:uid="{596887F0-4287-455C-9A5B-4694721ADAFC}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="18 Caracteres" sqref="H2" xr:uid="{CE192AB1-592B-4B0C-9218-6266C6ACEAB6}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Ej. 3328091659" sqref="I2" xr:uid="{4E7FC10B-B3C4-45DF-B679-0B873B6636FB}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Si son varios separados por coma" prompt="Escribirlos tal cual como viene en la base de datos._x000a_Ej. Paracetamol, DICLOFENACO" sqref="J2" xr:uid="{71A9E2C3-62D0-405B-8C58-39421C00968B}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/backend/volunteers/files/plantilla_voluntarios.xlsx
+++ b/backend/volunteers/files/plantilla_voluntarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perez\OneDrive - Universidad de Guadalajara\Desktop\gestion-voluntarios\backend\volunteers\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A30839A-F964-4B63-B6B0-F4D851112AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F3F85F-58F2-4EBE-90DA-6EA763C56BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33465" yWindow="4665" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6FE14DE-581F-47CE-BF18-0B4D8CFF29AB}" name="Tabla1" displayName="Tabla1" ref="A1:J2" insertRow="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6FE14DE-581F-47CE-BF18-0B4D8CFF29AB}" name="Tabla1" displayName="Tabla1" ref="A1:J2" totalsRowShown="0">
   <autoFilter ref="A1:J2" xr:uid="{B6FE14DE-581F-47CE-BF18-0B4D8CFF29AB}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{3D69406B-EFB1-45DE-897D-E7F378FA90DD}" name="Codigo"/>
